--- a/nebius/dist/20261007_Nebius收支模型_v0_2.xlsx
+++ b/nebius/dist/20261007_Nebius收支模型_v0_2.xlsx
@@ -37804,6 +37804,72 @@
       </rPr>
       <t xml:space="preserve">FCF×(1+g)÷(WACC−g)</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；常態化 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FCF ≤ 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">終值現值</t>
@@ -38089,24 +38155,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">WACC ≤ g </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">或常態化 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FCF ≤ 0</t>
+      <t xml:space="preserve">WACC ≤ g</t>
     </r>
     <r>
       <rPr>
@@ -38173,7 +38222,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。股權為負不算失效</t>
+      <t xml:space="preserve">。常態化 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FCF ≤ 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時終值以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">照常截斷並保留權重（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；股權為負不算失效</t>
     </r>
   </si>
   <si>
@@ -44369,35 +44494,73 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">WACC ≤ g </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">或常態化 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FCF ≤ 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；股權為負不算失效</t>
+      <t xml:space="preserve">WACC ≤ g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；常態化 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FCF ≤ 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時終值以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計、不算失效）；股權為負不算失效</t>
     </r>
   </si>
   <si>
@@ -45522,7 +45685,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">只改呈現（工作單 </t>
+      <t xml:space="preserve">工作單 </t>
     </r>
     <r>
       <rPr>
@@ -45539,7 +45702,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）：標題改為 </t>
+      <t xml:space="preserve">：標題改為 </t>
     </r>
     <r>
       <rPr>
@@ -45607,7 +45770,92 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">論點句改寫</t>
+      <t xml:space="preserve">論點句改寫；第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">輪：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">輸入改整數、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常態化 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FCF ≤ 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不再判失效（終值以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計、保留權重）</t>
     </r>
   </si>
   <si>
@@ -45620,58 +45868,109 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">無變動：保守 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$63.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、基準 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$61.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、積極 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$154.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（時間推移、實際數、假設、方法四項皆 </t>
+      <t xml:space="preserve">基準不變；保守 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$63.8 → $35.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(d) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失效口徑）、積極 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$154.6 → $154.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(c) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">假設：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整數）；時間推移、實際數皆 </t>
     </r>
     <r>
       <rPr>
@@ -45681,14 +45980,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -50390,7 +50681,7 @@
       </c>
       <c r="C21" s="77" t="n">
         <f aca="false">SUM(各期收支!C14:G14)</f>
-        <v>2.77833548720239</v>
+        <v>2.77912332452708</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50399,7 +50690,7 @@
       </c>
       <c r="C22" s="50" t="n">
         <f aca="false">各期收支!G14*12</f>
-        <v>9.02204111092379</v>
+        <v>9.0249877511024</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50408,7 +50699,7 @@
       </c>
       <c r="C23" s="78" t="n">
         <f aca="false">(C21+C22)/C20</f>
-        <v>0.978951277832951</v>
+        <v>0.979261087566013</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>1212</v>
@@ -50660,7 +50951,7 @@
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">各期收支!G20</f>
-        <v>1.34009001622121</v>
+        <v>1.34009043477806</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -50688,7 +50979,7 @@
       </c>
       <c r="G12" s="60" t="n">
         <f aca="false">G10-G11</f>
-        <v>-8.30205401622122</v>
+        <v>-8.30205443477806</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -50778,7 +51069,7 @@
       </c>
       <c r="G15" s="60" t="n">
         <f aca="false">G13-G14+MAX(0,-G12)</f>
-        <v>28.8454707918147</v>
+        <v>28.8454712103715</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -50837,7 +51128,7 @@
       </c>
       <c r="G17" s="35" t="n">
         <f aca="false">G12-G16</f>
-        <v>-8.30205401622122</v>
+        <v>-8.30205443477806</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -50943,19 +51234,19 @@
       </c>
       <c r="D21" s="28" t="n">
         <f aca="false">D20+各期收支!D77</f>
-        <v>0.339339353156743</v>
+        <v>0.339339355122895</v>
       </c>
       <c r="E21" s="28" t="n">
         <f aca="false">E20+各期收支!E77</f>
-        <v>0.381653473253443</v>
+        <v>0.381653482492194</v>
       </c>
       <c r="F21" s="28" t="n">
         <f aca="false">F20+各期收支!F77</f>
-        <v>0.412118608944017</v>
+        <v>0.412118628667715</v>
       </c>
       <c r="G21" s="28" t="n">
         <f aca="false">G20+各期收支!G77</f>
-        <v>0.48404810438509</v>
+        <v>0.484048124108787</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>1237</v>
@@ -50974,19 +51265,19 @@
       </c>
       <c r="D22" s="47" t="n">
         <f aca="false">D17/D21</f>
-        <v>-16.8617876523064</v>
+        <v>-16.8617875546082</v>
       </c>
       <c r="E22" s="47" t="n">
         <f aca="false">E17/E21</f>
-        <v>-15.5693166613843</v>
+        <v>-15.5693162844952</v>
       </c>
       <c r="F22" s="47" t="n">
         <f aca="false">F17/F21</f>
-        <v>-15.6235874582277</v>
+        <v>-15.6235867104942</v>
       </c>
       <c r="G22" s="47" t="n">
         <f aca="false">G17/G21</f>
-        <v>-17.1512995113734</v>
+        <v>-17.1512996772036</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>1239</v>
@@ -51234,7 +51525,7 @@
       </c>
       <c r="G32" s="60" t="n">
         <f aca="false">G11</f>
-        <v>1.34009001622121</v>
+        <v>1.34009043477806</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>1252</v>
@@ -51265,7 +51556,7 @@
       </c>
       <c r="G33" s="35" t="n">
         <f aca="false">G17</f>
-        <v>-8.30205401622122</v>
+        <v>-8.30205443477806</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -51293,7 +51584,7 @@
       </c>
       <c r="G34" s="61" t="n">
         <f aca="false">G33/G26</f>
-        <v>-0.190699257059208</v>
+        <v>-0.190699266673513</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -51309,19 +51600,19 @@
       </c>
       <c r="D35" s="80" t="n">
         <f aca="false">D17/D21</f>
-        <v>-16.8617876523064</v>
+        <v>-16.8617875546082</v>
       </c>
       <c r="E35" s="80" t="n">
         <f aca="false">E17/E21</f>
-        <v>-15.5693166613843</v>
+        <v>-15.5693162844952</v>
       </c>
       <c r="F35" s="80" t="n">
         <f aca="false">F17/F21</f>
-        <v>-15.6235874582277</v>
+        <v>-15.6235867104942</v>
       </c>
       <c r="G35" s="80" t="n">
         <f aca="false">G17/G21</f>
-        <v>-17.1512995113734</v>
+        <v>-17.1512996772036</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>1256</v>
@@ -51340,19 +51631,19 @@
       </c>
       <c r="D36" s="47" t="n">
         <f aca="false">(D17+輸入與假設!$C$148*輸入與假設!D$37)/D21</f>
-        <v>-16.4786903227728</v>
+        <v>-16.4786902272943</v>
       </c>
       <c r="E36" s="47" t="n">
         <f aca="false">(E17+輸入與假設!$C$148*輸入與假設!E$37)/E21</f>
-        <v>-15.228693533048</v>
+        <v>-15.2286931644044</v>
       </c>
       <c r="F36" s="47" t="n">
         <f aca="false">(F17+輸入與假設!$C$148*輸入與假設!F$37)/F21</f>
-        <v>-15.30814428925</v>
+        <v>-15.3081435566133</v>
       </c>
       <c r="G36" s="47" t="n">
         <f aca="false">(G17+輸入與假設!$C$148*輸入與假設!G$37)/G21</f>
-        <v>-16.8827311628512</v>
+        <v>-16.8827313396249</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>1258</v>
@@ -51821,7 +52112,7 @@
         <v>1286</v>
       </c>
       <c r="C21" s="50" t="n">
-        <f aca="false">IF(C30=1,0,C20*(1+輸入與假設!$C$135)/(輸入與假設!$C$134-輸入與假設!$C$135))</f>
+        <f aca="false">IF(OR(C30=1,C20&lt;=0),0,C20*(1+輸入與假設!$C$135)/(輸入與假設!$C$134-輸入與假設!$C$135))</f>
         <v>4.10566641699997</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -51898,7 +52189,7 @@
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">各期收支!C72/(1+輸入與假設!$C$134)^輸入與假設!$C$167+各期收支!D72/(1+輸入與假設!$C$134)^輸入與假設!$D$167+各期收支!E72/(1+輸入與假設!$C$134)^輸入與假設!$E$167+各期收支!F72/(1+輸入與假設!$C$134)^輸入與假設!$F$167+各期收支!G72/(1+輸入與假設!$C$134)^輸入與假設!$G$167</f>
-        <v>26.1631799874162</v>
+        <v>26.1631836220045</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>1297</v>
@@ -51910,7 +52201,7 @@
       </c>
       <c r="C29" s="83" t="n">
         <f aca="false">評價_DCF與目標價!$C$67+各期收支!G77</f>
-        <v>0.471014189553314</v>
+        <v>0.471014209277012</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -51918,7 +52209,7 @@
         <v>1299</v>
       </c>
       <c r="C30" s="42" t="n">
-        <f aca="false">IF(OR(輸入與假設!$C$134&lt;=輸入與假設!$C$135,C20&lt;=0),1,0)</f>
+        <f aca="false">IF(輸入與假設!$C$134&lt;=輸入與假設!$C$135,1,0)</f>
         <v>0</v>
       </c>
       <c r="I30" s="10" t="s">
@@ -52024,7 +52315,7 @@
       </c>
       <c r="C41" s="85" t="n">
         <f aca="false">INDEX(損益!$D$21:$G$21,1,輸入與假設!$C$142)</f>
-        <v>0.412118608944017</v>
+        <v>0.412118628667715</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>1314</v>
@@ -52048,7 +52339,7 @@
       </c>
       <c r="C43" s="41" t="n">
         <f aca="false">MAX(0,(C39-C40)/C41)*C42</f>
-        <v>112.218087544735</v>
+        <v>112.218082174059</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>1318</v>
@@ -52093,7 +52384,7 @@
       </c>
       <c r="C48" s="11" t="n">
         <f aca="false">C43*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52102,7 +52393,7 @@
       </c>
       <c r="C49" s="86" t="n">
         <f aca="false">SUM(C47:C48)</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>1324</v>
@@ -52123,7 +52414,7 @@
       </c>
       <c r="C51" s="27" t="n">
         <f aca="false">C49/C50-1</f>
-        <v>-0.752991763118404</v>
+        <v>-0.752991774940038</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52177,7 +52468,7 @@
       </c>
       <c r="C57" s="85" t="n">
         <f aca="false">C55+各期收支!G77</f>
-        <v>0.519335536354161</v>
+        <v>0.519335556077859</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52219,7 +52510,7 @@
       </c>
       <c r="C61" s="85" t="n">
         <f aca="false">C55*(1+輸入與假設!$C$147)^輸入與假設!$C$142+INDEX(各期收支!$D$77:$G$77,1,輸入與假設!$C$142)</f>
-        <v>0.461904140874276</v>
+        <v>0.461904160597974</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52228,7 +52519,7 @@
       </c>
       <c r="C62" s="11" t="n">
         <f aca="false">MAX(0,(C39-C60)/C61)*C42</f>
-        <v>115.051639040124</v>
+        <v>115.051634127322</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52237,7 +52528,7 @@
       </c>
       <c r="C63" s="82" t="n">
         <f aca="false">C59*(1+輸入與假設!$C$134)^輸入與假設!$C$159*IF(C30=1,0,輸入與假設!$C$143)+C62*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>63.2784014720682</v>
+        <v>63.278398770027</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52246,7 +52537,7 @@
       </c>
       <c r="C64" s="82" t="n">
         <f aca="false">MIN(輸入與假設!$C$124,C63)</f>
-        <v>63.2784014720682</v>
+        <v>63.278398770027</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>1343</v>
@@ -52339,7 +52630,7 @@
       </c>
       <c r="C73" s="11" t="n">
         <f aca="false">C49</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="I73" s="5" t="str">
         <f aca="false">"評等規則不變：空間 ≥"&amp;IF(ROUND(ABS(輸入與假設!$C$169)*100,4)=INT(ROUND(ABS(輸入與假設!$C$169)*100,4)),TEXT(ROUND(ABS(輸入與假設!$C$169)*100,4),"0"),TEXT(ROUND(ABS(輸入與假設!$C$169)*100,4),"0.0"))&amp;"%"&amp;" 且終值占比 &lt;"&amp;IF(ROUND(ABS(輸入與假設!$C$170)*100,4)=INT(ROUND(ABS(輸入與假設!$C$170)*100,4)),TEXT(ROUND(ABS(輸入與假設!$C$170)*100,4),"0"),TEXT(ROUND(ABS(輸入與假設!$C$170)*100,4),"0.0"))&amp;"%"&amp;"、股權募資 ≤"&amp;IF(輸入與假設!$C$172=INT(輸入與假設!$C$172),TEXT(輸入與假設!$C$172,"0"),TEXT(輸入與假設!$C$172,"0.0"))&amp;" 倍現市值 → 買進；空間 ≤−"&amp;IF(ROUND(ABS(輸入與假設!$C$171)*100,4)=INT(ROUND(ABS(輸入與假設!$C$171)*100,4)),TEXT(ROUND(ABS(輸入與假設!$C$171)*100,4),"0"),TEXT(ROUND(ABS(輸入與假設!$C$171)*100,4),"0.0"))&amp;"%"&amp;"，或股權募資 &gt;"&amp;IF(輸入與假設!$C$172=INT(輸入與假設!$C$172),TEXT(輸入與假設!$C$172,"0"),TEXT(輸入與假設!$C$172,"0.0"))&amp;" 倍且空間 ≤−"&amp;IF(ROUND(ABS(輸入與假設!$C$173)*100,4)=INT(ROUND(ABS(輸入與假設!$C$173)*100,4)),TEXT(ROUND(ABS(輸入與假設!$C$173)*100,4),"0"),TEXT(ROUND(ABS(輸入與假設!$C$173)*100,4),"0.0"))&amp;"%"&amp;" → 賣出；其餘中立"</f>
@@ -52361,7 +52652,7 @@
       </c>
       <c r="C75" s="15" t="n">
         <f aca="false">SUM(各期收支!C72:G72)/(輸入與假設!$C$124*輸入與假設!$C$125)</f>
-        <v>0.422837952875305</v>
+        <v>0.422838008469818</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52392,7 +52683,7 @@
       </c>
       <c r="C78" s="11" t="n">
         <f aca="false">輸入與假設!D201</f>
-        <v>63.8014107642874</v>
+        <v>35.1528258839757</v>
       </c>
       <c r="D78" s="8" t="n">
         <f aca="false">輸入與假設!E201</f>
@@ -52400,7 +52691,7 @@
       </c>
       <c r="E78" s="11" t="n">
         <f aca="false">C78-$C$77</f>
-        <v>-148.588089235713</v>
+        <v>-177.236674116024</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>1362</v>
@@ -52412,7 +52703,7 @@
       </c>
       <c r="C79" s="11" t="n">
         <f aca="false">輸入與假設!D202</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="D79" s="8" t="n">
         <f aca="false">輸入與假設!E202</f>
@@ -52420,7 +52711,7 @@
       </c>
       <c r="E79" s="11" t="n">
         <f aca="false">C79-$C$77</f>
-        <v>-150.669551850396</v>
+        <v>-150.669554804267</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52429,7 +52720,7 @@
       </c>
       <c r="C80" s="11" t="n">
         <f aca="false">輸入與假設!D203</f>
-        <v>154.558384092823</v>
+        <v>154.496343334039</v>
       </c>
       <c r="D80" s="8" t="n">
         <f aca="false">輸入與假設!E203</f>
@@ -52437,7 +52728,7 @@
       </c>
       <c r="E80" s="11" t="n">
         <f aca="false">C80-$C$77</f>
-        <v>-57.8311159071772</v>
+        <v>-57.8931566659612</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52446,11 +52737,11 @@
       </c>
       <c r="C81" s="11" t="n">
         <f aca="false">MIN(C78,C80)</f>
-        <v>63.8014107642874</v>
+        <v>35.1528258839757</v>
       </c>
       <c r="D81" s="11" t="n">
         <f aca="false">MAX(C78,C80)</f>
-        <v>154.558384092823</v>
+        <v>154.496343334039</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52472,11 +52763,11 @@
       </c>
       <c r="C83" s="11" t="n">
         <f aca="false">MIN(C46*IF(C30=1,0,輸入與假設!$C$143)+MAX(0,(C38*C82-C40)/C41)*C42*IF(C30=1,1,1-輸入與假設!$C$143),C46*IF(C30=1,0,輸入與假設!$C$143)+MAX(0,(C38*D82-C40)/C41)*C42*IF(C30=1,1,1-輸入與假設!$C$143))</f>
-        <v>44.8818263998867</v>
+        <v>44.8818242518752</v>
       </c>
       <c r="D83" s="11" t="n">
         <f aca="false">MAX(C46*IF(C30=1,0,輸入與假設!$C$143)+MAX(0,(C38*C82-C40)/C41)*C42*IF(C30=1,1,1-輸入與假設!$C$143),C46*IF(C30=1,0,輸入與假設!$C$143)+MAX(0,(C38*D82-C40)/C41)*C42*IF(C30=1,1,1-輸入與假設!$C$143))</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>1368</v>
@@ -52488,7 +52779,7 @@
       </c>
       <c r="C84" s="11" t="n">
         <f aca="false">C43</f>
-        <v>112.218087544735</v>
+        <v>112.218082174059</v>
       </c>
       <c r="D84" s="8" t="n">
         <f aca="false">IF(AND((C43/MAX(輸入與假設!$C$124,0.01)-1)&gt;=輸入與假設!$C$169,$C$74&lt;輸入與假設!$C$170,$C$75&lt;=輸入與假設!$C$172),1,IF(OR((C43/MAX(輸入與假設!$C$124,0.01)-1)&lt;=輸入與假設!$C$171,AND($C$75&gt;輸入與假設!$C$172,(C43/MAX(輸入與假設!$C$124,0.01)-1)&lt;=輸入與假設!$C$173)),-1,0))</f>
@@ -52505,7 +52796,7 @@
       </c>
       <c r="C85" s="11" t="n">
         <f aca="false">(C25+C28)/C29</f>
-        <v>-53.0762185174513</v>
+        <v>-53.0762085783718</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52514,7 +52805,7 @@
       </c>
       <c r="C86" s="3" t="str">
         <f aca="false">"目標價 $"&amp;TEXT(C49,"0.0")&amp;"（情境區間 $"&amp;TEXT(C81,"0.0")&amp;"–$"&amp;TEXT(D81,"0.0")&amp;"）"</f>
-        <v>目標價 $61.7（情境區間 $63.8–$154.6）</v>
+        <v>目標價 $61.7（情境區間 $35.2–$154.5）</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52541,7 +52832,7 @@
       </c>
       <c r="C89" s="3" t="str">
         <f aca="false">IF(D81&lt;輸入與假設!$C$124,"情境區間上緣 $"&amp;TEXT(D81,"0.0")&amp;" 低於現價 $"&amp;TEXT(輸入與假設!$C$124,"0.00")&amp;IF((D78&lt;&gt;-1)+(D79&lt;&gt;-1)+(D80&lt;&gt;-1)&gt;0,"，但"&amp;SUBSTITUTE(TRIM(IF(D78&lt;&gt;-1,"保守","")&amp;" "&amp;IF(D79&lt;&gt;-1,"基準","")&amp;" "&amp;IF(D80&lt;&gt;-1,"積極",""))," ","、")&amp;"情境未達賣出門檻 $"&amp;TEXT($C$77,"0.0"),"：賣出在三個擴張情境下都成立"),"情境區間上緣 $"&amp;TEXT(D81,"0.0")&amp;" 不低於現價 $"&amp;TEXT(輸入與假設!$C$124,"0.00")&amp;"：賣出並非在三個擴張情境下都成立")&amp;"。"&amp;IF(ABS(E78)&lt;輸入與假設!$C$174*輸入與假設!$C$124,"保守情境 $"&amp;TEXT(C78,"0.0")&amp;"，"&amp;IF(E78&lt;0,"距賣出門檻","高於賣出門檻")&amp;" $"&amp;TEXT($C$77,"0.0")&amp;" 僅 $"&amp;TEXT(ABS(E78),"0.0")&amp;"。","")&amp;IF(ABS(E79)&lt;輸入與假設!$C$174*輸入與假設!$C$124,"基準情境 $"&amp;TEXT(C79,"0.0")&amp;"，"&amp;IF(E79&lt;0,"距賣出門檻","高於賣出門檻")&amp;" $"&amp;TEXT($C$77,"0.0")&amp;" 僅 $"&amp;TEXT(ABS(E79),"0.0")&amp;"。","")&amp;IF(ABS(E80)&lt;輸入與假設!$C$174*輸入與假設!$C$124,"積極情境 $"&amp;TEXT(C80,"0.0")&amp;"，"&amp;IF(E80&lt;0,"距賣出門檻","高於賣出門檻")&amp;" $"&amp;TEXT($C$77,"0.0")&amp;" 僅 $"&amp;TEXT(ABS(E80),"0.0")&amp;"。","")</f>
-        <v>情境區間上緣 $154.6 低於現價 $249.87：賣出在三個擴張情境下都成立。</v>
+        <v>情境區間上緣 $154.5 低於現價 $249.87：賣出在三個擴張情境下都成立。</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52592,15 +52883,15 @@
       </c>
       <c r="D93" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,2)*$B93-(INDEX(各期收支!$D$82:$G$82,1,2)-INDEX(各期收支!$D$47:$G$47,1,2)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,2))/(1+輸入與假設!$C$134)^(2-輸入與假設!$C$163)</f>
-        <v>8.87187102849463</v>
+        <v>8.87187081373173</v>
       </c>
       <c r="E93" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,3)*$B93-(INDEX(各期收支!$D$82:$G$82,1,3)-INDEX(各期收支!$D$47:$G$47,1,3)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,3))/(1+輸入與假設!$C$134)^(3-輸入與假設!$C$163)</f>
-        <v>32.6196938187969</v>
+        <v>32.6196922576421</v>
       </c>
       <c r="F93" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,4)*$B93-(INDEX(各期收支!$D$82:$G$82,1,4)-INDEX(各期收支!$D$47:$G$47,1,4)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,4))/(1+輸入與假設!$C$134)^(4-輸入與假設!$C$163)</f>
-        <v>42.9579123899208</v>
+        <v>42.9579056385282</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52616,15 +52907,15 @@
       </c>
       <c r="D94" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,2)*$B94-(INDEX(各期收支!$D$82:$G$82,1,2)-INDEX(各期收支!$D$47:$G$47,1,2)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,2))/(1+輸入與假設!$C$134)^(2-輸入與假設!$C$163)</f>
-        <v>35.8329456874982</v>
+        <v>35.832944820084</v>
       </c>
       <c r="E94" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,3)*$B94-(INDEX(各期收支!$D$82:$G$82,1,3)-INDEX(各期收支!$D$47:$G$47,1,3)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,3))/(1+輸入與假設!$C$134)^(3-輸入與假設!$C$163)</f>
-        <v>66.2959373182324</v>
+        <v>66.2959341453571</v>
       </c>
       <c r="F94" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,4)*$B94-(INDEX(各期收支!$D$82:$G$82,1,4)-INDEX(各期收支!$D$47:$G$47,1,4)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,4))/(1+輸入與假設!$C$134)^(4-輸入與假設!$C$163)</f>
-        <v>75.2285946517858</v>
+        <v>75.2285865854471</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52640,15 +52931,15 @@
       </c>
       <c r="D95" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,2)*$B95-(INDEX(各期收支!$D$82:$G$82,1,2)-INDEX(各期收支!$D$47:$G$47,1,2)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,2))/(1+輸入與假設!$C$134)^(2-輸入與假設!$C$163)</f>
-        <v>48.087979623409</v>
+        <v>48.087978459335</v>
       </c>
       <c r="E95" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,3)*$B95-(INDEX(各期收支!$D$82:$G$82,1,3)-INDEX(各期收支!$D$47:$G$47,1,3)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,3))/(1+輸入與假設!$C$134)^(3-輸入與假設!$C$163)</f>
-        <v>81.6033207270667</v>
+        <v>81.6033168215912</v>
       </c>
       <c r="F95" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,4)*$B95-(INDEX(各期收支!$D$82:$G$82,1,4)-INDEX(各期收支!$D$47:$G$47,1,4)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,4))/(1+輸入與假設!$C$134)^(4-輸入與假設!$C$163)</f>
-        <v>89.8970865889971</v>
+        <v>89.8970779249556</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52660,19 +52951,19 @@
       </c>
       <c r="C96" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,1)*$B96-(INDEX(各期收支!$D$82:$G$82,1,1)-INDEX(各期收支!$D$47:$G$47,1,1)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,1))/(1+輸入與假設!$C$134)^(1-輸入與假設!$C$163)</f>
-        <v>10.4977709371744</v>
+        <v>10.4977708763497</v>
       </c>
       <c r="D96" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,2)*$B96-(INDEX(各期收支!$D$82:$G$82,1,2)-INDEX(各期收支!$D$47:$G$47,1,2)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,2))/(1+輸入與假設!$C$134)^(2-輸入與假設!$C$163)</f>
-        <v>72.5980474952304</v>
+        <v>72.5980457378371</v>
       </c>
       <c r="E96" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,3)*$B96-(INDEX(各期收支!$D$82:$G$82,1,3)-INDEX(各期收支!$D$47:$G$47,1,3)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,3))/(1+輸入與假設!$C$134)^(3-輸入與假設!$C$163)</f>
-        <v>112.218087544735</v>
+        <v>112.218082174059</v>
       </c>
       <c r="F96" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,4)*$B96-(INDEX(各期收支!$D$82:$G$82,1,4)-INDEX(各期收支!$D$47:$G$47,1,4)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,4))/(1+輸入與假設!$C$134)^(4-輸入與假設!$C$163)</f>
-        <v>119.23407046342</v>
+        <v>119.234060603973</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52684,19 +52975,19 @@
       </c>
       <c r="C97" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,1)*$B97-(INDEX(各期收支!$D$82:$G$82,1,1)-INDEX(各期收支!$D$47:$G$47,1,1)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,1))/(1+輸入與假設!$C$134)^(1-輸入與假設!$C$163)</f>
-        <v>24.9204668921262</v>
+        <v>24.9204667477355</v>
       </c>
       <c r="D97" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,2)*$B97-(INDEX(各期收支!$D$82:$G$82,1,2)-INDEX(各期收支!$D$47:$G$47,1,2)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,2))/(1+輸入與假設!$C$134)^(2-輸入與假設!$C$163)</f>
-        <v>97.1081153670519</v>
+        <v>97.1081130163391</v>
       </c>
       <c r="E97" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,3)*$B97-(INDEX(各期收支!$D$82:$G$82,1,3)-INDEX(各期收支!$D$47:$G$47,1,3)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,3))/(1+輸入與假設!$C$134)^(3-輸入與假設!$C$163)</f>
-        <v>142.832854362404</v>
+        <v>142.832847526528</v>
       </c>
       <c r="F97" s="11" t="n">
         <f aca="false">MAX(0,(INDEX(損益!$D$19:$G$19,1,4)*$B97-(INDEX(各期收支!$D$82:$G$82,1,4)-INDEX(各期收支!$D$47:$G$47,1,4)+評價_DCF與目標價!$C$69))/INDEX(損益!$D$21:$G$21,1,4))/(1+輸入與假設!$C$134)^(4-輸入與假設!$C$163)</f>
-        <v>148.571054337843</v>
+        <v>148.57104328299</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false"/>
@@ -52733,15 +53024,15 @@
       </c>
       <c r="D100" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+D93*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>4.87952906567205</v>
+        <v>4.87952894755245</v>
       </c>
       <c r="E100" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+E93*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>17.9408316003383</v>
+        <v>17.9408307417031</v>
       </c>
       <c r="F100" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+F93*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>23.6268518144565</v>
+        <v>23.6268481011905</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52757,15 +53048,15 @@
       </c>
       <c r="D101" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+D94*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>19.708120128124</v>
+        <v>19.7081196510462</v>
       </c>
       <c r="E101" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+E94*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>36.4627655250278</v>
+        <v>36.4627637799464</v>
       </c>
       <c r="F101" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+F94*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>41.3757270584822</v>
+        <v>41.3757226219959</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52781,15 +53072,15 @@
       </c>
       <c r="D102" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+D95*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>26.4483887928749</v>
+        <v>26.4483881526343</v>
       </c>
       <c r="E102" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+E95*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>44.8818263998867</v>
+        <v>44.8818242518752</v>
       </c>
       <c r="F102" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+F95*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>49.4433976239484</v>
+        <v>49.4433928587256</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52801,19 +53092,19 @@
       </c>
       <c r="C103" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+C96*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>5.7737740154459</v>
+        <v>5.77377398199232</v>
       </c>
       <c r="D103" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+D96*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>39.9289261223767</v>
+        <v>39.9289251558104</v>
       </c>
       <c r="E103" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+E96*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="F103" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+F96*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>65.5787387548809</v>
+        <v>65.5787333321851</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -52825,19 +53116,19 @@
       </c>
       <c r="C104" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+C97*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>13.7062567906694</v>
+        <v>13.7062567112545</v>
       </c>
       <c r="D104" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+D97*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>53.4094634518785</v>
+        <v>53.4094621589865</v>
       </c>
       <c r="E104" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+E97*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>78.5580698993223</v>
+        <v>78.5580661395902</v>
       </c>
       <c r="F104" s="11" t="n">
         <f aca="false">C46*IF(C30=1,0,輸入與假設!$C$143)+F97*IF(C30=1,1,1-輸入與假設!$C$143)</f>
-        <v>81.7140798858134</v>
+        <v>81.7140738056445</v>
       </c>
     </row>
   </sheetData>
@@ -53696,7 +53987,7 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">資產負債_租賃承諾!C23</f>
-        <v>0.978951277832951</v>
+        <v>0.979261087566013</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>1476</v>
@@ -53814,7 +54105,7 @@
       </c>
       <c r="B16" s="50" t="n">
         <f aca="false">(運營_產能與收入!D37+運營_產能與收入!D38+輸入與假設!D54-各期收支!D15)+(運營_產能與收入!D32+運營_產能與收入!D23*輸入與假設!D44*(1-輸入與假設!D45))*運營_產能與收入!D36-損益!D19</f>
-        <v>0.141</v>
+        <v>0.140999999999999</v>
       </c>
       <c r="C16" s="5" t="n">
         <f aca="false">0</f>
@@ -53872,7 +54163,7 @@
       </c>
       <c r="B19" s="97" t="n">
         <f aca="false">SUM(各期收支!C72:G72)/(輸入與假設!$C$124*輸入與假設!$C$125)</f>
-        <v>0.422837952875305</v>
+        <v>0.422838008469818</v>
       </c>
       <c r="C19" s="5" t="str">
         <f aca="false">"≤"&amp;IF(輸入與假設!$C$172=INT(輸入與假設!$C$172),TEXT(輸入與假設!$C$172,"0"),TEXT(輸入與假設!$C$172,"0.0"))&amp;"x"</f>
@@ -53951,7 +54242,7 @@
       </c>
       <c r="B23" s="50" t="n">
         <f aca="false">運營_站點!G27</f>
-        <v>0.357747035699154</v>
+        <v>0.357835364241679</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>1504</v>
@@ -53970,7 +54261,7 @@
       </c>
       <c r="B24" s="50" t="n">
         <f aca="false">運營_站點!$C$31</f>
-        <v>-3.82343548720239</v>
+        <v>-3.82422332452708</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>1507</v>
@@ -54050,7 +54341,7 @@
       </c>
       <c r="B32" s="9" t="n">
         <f aca="false">SUM(各期收支!C15:G15)</f>
-        <v>3.82343548720239</v>
+        <v>3.82422332452708</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54059,7 +54350,7 @@
       </c>
       <c r="B33" s="9" t="n">
         <f aca="false">SUM(各期收支!C20:G20)</f>
-        <v>4.73288889181467</v>
+        <v>4.73288931037151</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54077,7 +54368,7 @@
       </c>
       <c r="B35" s="9" t="n">
         <f aca="false">SUM(各期收支!C45:G45)-(輸入與假設!$C$179-輸入與假設!$C$180-輸入與假設!$C$182)</f>
-        <v>-73.9042973928621</v>
+        <v>-73.9043053163601</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54086,7 +54377,7 @@
       </c>
       <c r="B36" s="9" t="n">
         <f aca="false">SUM(各期收支!C45:G45)</f>
-        <v>-77.7820973928621</v>
+        <v>-77.7821053163601</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54113,7 +54404,7 @@
       </c>
       <c r="B39" s="11" t="n">
         <f aca="false">評價_DCF與目標價!C49</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
     </row>
   </sheetData>
@@ -54170,7 +54461,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="100" t="s">
         <v>1529</v>
       </c>
@@ -54422,7 +54713,7 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">評價_DCF與目標價!C49</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54446,7 +54737,7 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">C7/C8-1</f>
-        <v>-0.752991763118404</v>
+        <v>-0.752991774940038</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54458,11 +54749,11 @@
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">評價_DCF與目標價!C81</f>
-        <v>63.8014107642874</v>
+        <v>35.1528258839757</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">評價_DCF與目標價!D81</f>
-        <v>154.558384092823</v>
+        <v>154.496343334039</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54474,11 +54765,11 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">評價_DCF與目標價!C83</f>
-        <v>44.8818263998867</v>
+        <v>44.8818242518752</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">評價_DCF與目標價!D83</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54502,7 +54793,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">C7-C12</f>
-        <v>-150.669551850396</v>
+        <v>-150.669554804267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54511,7 +54802,7 @@
       </c>
       <c r="C14" s="9" t="str">
         <f aca="false">C6&amp;"：點位 $"&amp;TEXT(C7,"0.0")&amp;"，較現價 $"&amp;TEXT(C8,"0.00")&amp;" "&amp;IF(C9&gt;=0,"高","低")&amp;" "&amp;TEXT(ABS(C9)*100,"0")&amp;"%；情境區間 $"&amp;TEXT(C10,"0.0")&amp;"–$"&amp;TEXT(D10,"0.0")&amp;"，方法區間 $"&amp;TEXT(C11,"0.0")&amp;"–$"&amp;TEXT(D11,"0.0")&amp;"；點位"&amp;IF(C13&lt;0,"低於","高於")&amp;"賣出門檻 $"&amp;TEXT(C12,"0.0")&amp;" 達 $"&amp;TEXT(ABS(C13),"0.0")&amp;"。"</f>
-        <v>賣出：點位 $61.7，較現價 $249.87 低 75%；情境區間 $63.8–$154.6，方法區間 $44.9–$61.7；點位低於賣出門檻 $212.4 達 $150.7。</v>
+        <v>賣出：點位 $61.7，較現價 $249.87 低 75%；情境區間 $35.2–$154.5，方法區間 $44.9–$61.7；點位低於賣出門檻 $212.4 達 $150.7。</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -54520,7 +54811,7 @@
       </c>
       <c r="C15" s="9" t="str">
         <f aca="false">評價_DCF與目標價!C89</f>
-        <v>情境區間上緣 $154.6 低於現價 $249.87：賣出在三個擴張情境下都成立。</v>
+        <v>情境區間上緣 $154.5 低於現價 $249.87：賣出在三個擴張情境下都成立。</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55760,10 +56051,10 @@
         <v>5000</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>5833.3333</v>
+        <v>5833</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>6666.6667</v>
+        <v>6667</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>7500</v>
@@ -55780,7 +56071,7 @@
         <v>147</v>
       </c>
       <c r="C16" s="20" t="n">
-        <v>833.3333</v>
+        <v>833</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>148</v>
@@ -55799,22 +56090,22 @@
       </c>
       <c r="D17" s="21" t="n">
         <f aca="false">MIN(D15,C17+輸入與假設!$C$16*D$37)</f>
-        <v>1583.3333</v>
+        <v>1583</v>
       </c>
       <c r="E17" s="21" t="n">
         <f aca="false">MIN(E15,D17+輸入與假設!$C$16*E$37)</f>
-        <v>2416.6666</v>
+        <v>2416</v>
       </c>
       <c r="F17" s="21" t="n">
         <f aca="false">MIN(F15,E17+輸入與假設!$C$16*F$37)</f>
-        <v>3249.9999</v>
+        <v>3249</v>
       </c>
       <c r="G17" s="21" t="n">
         <f aca="false">MIN(G15,F17+輸入與假設!$C$16*G$37)</f>
-        <v>4083.3332</v>
+        <v>4082</v>
       </c>
       <c r="I17" s="20" t="n">
-        <v>833.3333</v>
+        <v>833</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>158</v>
@@ -56997,19 +57288,19 @@
       </c>
       <c r="D77" s="31" t="n">
         <f aca="false">D23*MAX(0,D39-輸入與假設!$C$24)/(D17-輸入與假設!$C$24)</f>
-        <v>0.420000008842105</v>
+        <v>0.42008843967151</v>
       </c>
       <c r="E77" s="31" t="n">
         <f aca="false">E23*MAX(0,E39-輸入與假設!$C$24)/(E17-輸入與假設!$C$24)</f>
-        <v>0.790344849388823</v>
+        <v>0.790562913907285</v>
       </c>
       <c r="F77" s="31" t="n">
         <f aca="false">F23*MAX(0,F39-輸入與假設!$C$24)/(F17-輸入與假設!$C$24)</f>
-        <v>0.766153869727811</v>
+        <v>0.766389658356417</v>
       </c>
       <c r="G77" s="31" t="n">
         <f aca="false">G23*MAX(0,G39-輸入與假設!$C$24)/(G17-輸入與假設!$C$24)</f>
-        <v>0.751836759243649</v>
+        <v>0.752082312591867</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>264</v>
@@ -58909,7 +59200,7 @@
       </c>
       <c r="D200" s="11" t="n">
         <f aca="false">評價_DCF與目標價!C49</f>
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="E200" s="8" t="n">
         <f aca="false">評價_DCF與目標價!C76</f>
@@ -58925,7 +59216,7 @@
       </c>
       <c r="D201" s="41" t="n">
         <f t="dataTable" ref="D201:E203" dt2D="0" dtr="0" r1="C5"/>
-        <v>63.8014107642874</v>
+        <v>35.1528258839757</v>
       </c>
       <c r="E201" s="42" t="n">
         <v>-1</v>
@@ -58939,7 +59230,7 @@
         <v>2</v>
       </c>
       <c r="D202" s="41" t="n">
-        <v>61.7199481496045</v>
+        <v>61.7199451957327</v>
       </c>
       <c r="E202" s="42" t="n">
         <v>-1</v>
@@ -58953,7 +59244,7 @@
         <v>3</v>
       </c>
       <c r="D203" s="41" t="n">
-        <v>154.558384092823</v>
+        <v>154.496343334039</v>
       </c>
       <c r="E203" s="42" t="n">
         <v>-1</v>
@@ -61119,19 +61410,19 @@
       </c>
       <c r="D14" s="38" t="n">
         <f aca="false">輸入與假設!D$77</f>
-        <v>0.420000008842105</v>
+        <v>0.42008843967151</v>
       </c>
       <c r="E14" s="38" t="n">
         <f aca="false">輸入與假設!E$77</f>
-        <v>0.790344849388823</v>
+        <v>0.790562913907285</v>
       </c>
       <c r="F14" s="38" t="n">
         <f aca="false">輸入與假設!F$77</f>
-        <v>0.766153869727811</v>
+        <v>0.766389658356417</v>
       </c>
       <c r="G14" s="38" t="n">
         <f aca="false">輸入與假設!G$77</f>
-        <v>0.751836759243649</v>
+        <v>0.752082312591867</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>657</v>
@@ -61150,19 +61441,19 @@
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">D13+D14</f>
-        <v>0.655200008842105</v>
+        <v>0.65528843967151</v>
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">E13+E14</f>
-        <v>1.02454484938882</v>
+        <v>1.02476291390728</v>
       </c>
       <c r="F15" s="31" t="n">
         <f aca="false">F13+F14</f>
-        <v>1.00755386972781</v>
+        <v>1.00778965835642</v>
       </c>
       <c r="G15" s="31" t="n">
         <f aca="false">G13+G14</f>
-        <v>0.994536759243649</v>
+        <v>0.994782312591867</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -61284,7 +61575,7 @@
       </c>
       <c r="G19" s="31" t="n">
         <f aca="false">G74</f>
-        <v>1.22796501622121</v>
+        <v>1.22796543477806</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>665</v>
@@ -61315,7 +61606,7 @@
       </c>
       <c r="G20" s="31" t="n">
         <f aca="false">G16+G19</f>
-        <v>1.34009001622121</v>
+        <v>1.34009043477806</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -61483,19 +61774,19 @@
       </c>
       <c r="D26" s="35" t="n">
         <f aca="false">D12+D15+D20+D21+D22+D23+D24+D25</f>
-        <v>30.7513754738421</v>
+        <v>30.7514639046715</v>
       </c>
       <c r="E26" s="35" t="n">
         <f aca="false">E12+E15+E20+E21+E22+E23+E24+E25</f>
-        <v>31.2939469793888</v>
+        <v>31.2941650439073</v>
       </c>
       <c r="F26" s="35" t="n">
         <f aca="false">F12+F15+F20+F21+F22+F23+F24+F25</f>
-        <v>31.3819559997278</v>
+        <v>31.3821917883564</v>
       </c>
       <c r="G26" s="35" t="n">
         <f aca="false">G12+G15+G20+G21+G22+G23+G24+G25</f>
-        <v>43.8246267754649</v>
+        <v>43.8248727473699</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>677</v>
@@ -61557,19 +61848,19 @@
       </c>
       <c r="D29" s="38" t="n">
         <f aca="false">運營_產能與收入!D37</f>
-        <v>3.69896300435364</v>
+        <v>3.69901795601495</v>
       </c>
       <c r="E29" s="38" t="n">
         <f aca="false">運營_產能與收入!E37</f>
-        <v>3.73565292703846</v>
+        <v>3.73572048460084</v>
       </c>
       <c r="F29" s="38" t="n">
         <f aca="false">運營_產能與收入!F37</f>
-        <v>3.75607222237366</v>
+        <v>3.75612302615044</v>
       </c>
       <c r="G29" s="38" t="n">
         <f aca="false">運營_產能與收入!G37</f>
-        <v>2.91937250904087</v>
+        <v>2.9194059199878</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -61585,19 +61876,19 @@
       </c>
       <c r="D30" s="38" t="n">
         <f aca="false">運營_產能與收入!D38</f>
-        <v>2.22382161769426</v>
+        <v>2.2238546547082</v>
       </c>
       <c r="E30" s="38" t="n">
         <f aca="false">運營_產能與收入!E38</f>
-        <v>8.23197479835494</v>
+        <v>8.23212366982714</v>
       </c>
       <c r="F30" s="38" t="n">
         <f aca="false">運營_產能與收入!F38</f>
-        <v>13.5021471986569</v>
+        <v>13.5023298256224</v>
       </c>
       <c r="G30" s="38" t="n">
         <f aca="false">運營_產能與收入!G38</f>
-        <v>18.2683215907122</v>
+        <v>18.2685306636967</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -61731,19 +62022,19 @@
       </c>
       <c r="D35" s="35" t="n">
         <f aca="false">D28+D29+D30+D31+D32+D33+D34</f>
-        <v>12.6578546776035</v>
+        <v>12.6579426662787</v>
       </c>
       <c r="E35" s="35" t="n">
         <f aca="false">E28+E29+E30+E31+E32+E33+E34</f>
-        <v>16.4576744290971</v>
+        <v>16.4578908581317</v>
       </c>
       <c r="F35" s="35" t="n">
         <f aca="false">F28+F29+F30+F31+F32+F33+F34</f>
-        <v>20.267250556833</v>
+        <v>20.2674839875753</v>
       </c>
       <c r="G35" s="35" t="n">
         <f aca="false">G28+G29+G30+G31+G32+G33+G34</f>
-        <v>23.2250481902881</v>
+        <v>23.2252906742195</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -61883,15 +62174,15 @@
       </c>
       <c r="D40" s="31" t="n">
         <f aca="false">D72</f>
-        <v>3.40217981449877</v>
+        <v>3.40218025665292</v>
       </c>
       <c r="E40" s="31" t="n">
         <f aca="false">E72</f>
-        <v>8.78663155029171</v>
+        <v>8.7866331857756</v>
       </c>
       <c r="F40" s="31" t="n">
         <f aca="false">F72</f>
-        <v>6.11470544289481</v>
+        <v>6.11470780078109</v>
       </c>
       <c r="G40" s="31" t="n">
         <f aca="false">G72</f>
@@ -61926,7 +62217,7 @@
       </c>
       <c r="G41" s="31" t="n">
         <f aca="false">G73</f>
-        <v>0.167607385176778</v>
+        <v>0.16761087315047</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>701</v>
@@ -61945,19 +62236,19 @@
       </c>
       <c r="D42" s="35" t="n">
         <f aca="false">D35+D36+D37+D38+D39+D40+D41</f>
-        <v>30.7513754738421</v>
+        <v>30.7514639046715</v>
       </c>
       <c r="E42" s="35" t="n">
         <f aca="false">E35+E36+E37+E38+E39+E40+E41</f>
-        <v>31.2939469793888</v>
+        <v>31.2941650439073</v>
       </c>
       <c r="F42" s="35" t="n">
         <f aca="false">F35+F36+F37+F38+F39+F40+F41</f>
-        <v>31.3819559997278</v>
+        <v>31.3821917883564</v>
       </c>
       <c r="G42" s="35" t="n">
         <f aca="false">G35+G36+G37+G38+G39+G40+G41</f>
-        <v>43.8246267754649</v>
+        <v>43.8248727473699</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62016,19 +62307,19 @@
       </c>
       <c r="D45" s="35" t="n">
         <f aca="false">D35-(D26-D24-D25)</f>
-        <v>-18.0935207962387</v>
+        <v>-18.0935212383928</v>
       </c>
       <c r="E45" s="35" t="n">
         <f aca="false">E35-(E26-E24-E25)</f>
-        <v>-14.8362725502917</v>
+        <v>-14.8362741857756</v>
       </c>
       <c r="F45" s="35" t="n">
         <f aca="false">F35-(F26-F24-F25)</f>
-        <v>-11.1147054428948</v>
+        <v>-11.1147078007811</v>
       </c>
       <c r="G45" s="35" t="n">
         <f aca="false">G35-(G26-G24-G25)</f>
-        <v>-16.8045785851768</v>
+        <v>-16.8045820731505</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>707</v>
@@ -62118,19 +62409,19 @@
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">D12+D15+D16+D21+D22+D23+D24+D25</f>
-        <v>29.9267500088421</v>
+        <v>29.9268384396715</v>
       </c>
       <c r="E50" s="31" t="n">
         <f aca="false">E12+E15+E16+E21+E22+E23+E24+E25</f>
-        <v>30.2960948493888</v>
+        <v>30.2963129139073</v>
       </c>
       <c r="F50" s="31" t="n">
         <f aca="false">F12+F15+F16+F21+F22+F23+F24+F25</f>
-        <v>30.2791038697278</v>
+        <v>30.2793396583564</v>
       </c>
       <c r="G50" s="31" t="n">
         <f aca="false">G12+G15+G16+G21+G22+G23+G24+G25</f>
-        <v>42.5966617592437</v>
+        <v>42.5969073125919</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>713</v>
@@ -62317,19 +62608,19 @@
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">D17+D35+D36+D37+D44-D50-D52*D51-D56*D53-D55*D54</f>
-        <v>-15.3585836324256</v>
+        <v>-15.3585840745797</v>
       </c>
       <c r="E57" s="31" t="n">
         <f aca="false">E17+E35+E36+E37+E44-E50-E52*E51-E56*E53-E55*E54</f>
-        <v>-12.6630458852917</v>
+        <v>-12.6630475207756</v>
       </c>
       <c r="F57" s="31" t="n">
         <f aca="false">F17+F35+F36+F37+F44-F50-F52*F51-F56*F53-F55*F54</f>
-        <v>-9.00970544289481</v>
+        <v>-9.00970780078109</v>
       </c>
       <c r="G57" s="31" t="n">
         <f aca="false">G17+G35+G36+G37+G44-G50-G52*G51-G56*G53-G55*G54</f>
-        <v>-18.4744656989556</v>
+        <v>-18.4744687683724</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -62345,19 +62636,19 @@
       </c>
       <c r="D58" s="35" t="n">
         <f aca="false">MAX(0,輸入與假設!$C$102-D57)</f>
-        <v>17.3585836324256</v>
+        <v>17.3585840745797</v>
       </c>
       <c r="E58" s="35" t="n">
         <f aca="false">MAX(0,輸入與假設!$C$102-E57)</f>
-        <v>14.6630458852917</v>
+        <v>14.6630475207756</v>
       </c>
       <c r="F58" s="35" t="n">
         <f aca="false">MAX(0,輸入與假設!$C$102-F57)</f>
-        <v>11.0097054428948</v>
+        <v>11.0097078007811</v>
       </c>
       <c r="G58" s="35" t="n">
         <f aca="false">MAX(0,輸入與假設!$C$102-G57)</f>
-        <v>20.4744656989556</v>
+        <v>20.4744687683724</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -62612,19 +62903,19 @@
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">MAX(0,D58+D52*D66-D66)</f>
-        <v>8.29717981449877</v>
+        <v>8.29718025665292</v>
       </c>
       <c r="E67" s="31" t="n">
         <f aca="false">MAX(0,E58+E52*E66-E66)</f>
-        <v>13.6816315502917</v>
+        <v>13.6816331857756</v>
       </c>
       <c r="F67" s="31" t="n">
         <f aca="false">MAX(0,F58+F52*F66-F66)</f>
-        <v>11.0097054428948</v>
+        <v>11.0097078007811</v>
       </c>
       <c r="G67" s="31" t="n">
         <f aca="false">MAX(0,G58+G52*G66-G66)</f>
-        <v>20.4744656989556</v>
+        <v>20.4744687683724</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -62702,19 +62993,19 @@
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">MAX(0,D67+D55*D69-D69)</f>
-        <v>3.40217981449877</v>
+        <v>3.40218025665292</v>
       </c>
       <c r="E70" s="31" t="n">
         <f aca="false">MAX(0,E67+E55*E69-E69)</f>
-        <v>8.78663155029171</v>
+        <v>8.7866331857756</v>
       </c>
       <c r="F70" s="31" t="n">
         <f aca="false">MAX(0,F67+F55*F69-F69)</f>
-        <v>6.11470544289481</v>
+        <v>6.11470780078109</v>
       </c>
       <c r="G70" s="31" t="n">
         <f aca="false">MAX(0,G67+G55*G69-G69)</f>
-        <v>15.5794656989556</v>
+        <v>15.5794687683724</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -62761,15 +63052,15 @@
       </c>
       <c r="D72" s="35" t="n">
         <f aca="false">MIN(D70,D71)</f>
-        <v>3.40217981449877</v>
+        <v>3.40218025665292</v>
       </c>
       <c r="E72" s="35" t="n">
         <f aca="false">MIN(E70,E71)</f>
-        <v>8.78663155029171</v>
+        <v>8.7866331857756</v>
       </c>
       <c r="F72" s="35" t="n">
         <f aca="false">MIN(F70,F71)</f>
-        <v>6.11470544289481</v>
+        <v>6.11470780078109</v>
       </c>
       <c r="G72" s="35" t="n">
         <f aca="false">MIN(G70,G71)</f>
@@ -62801,7 +63092,7 @@
       </c>
       <c r="G73" s="35" t="n">
         <f aca="false">(G70-G72)/(1-G56)</f>
-        <v>0.167607385176778</v>
+        <v>0.16761087315047</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -62829,7 +63120,7 @@
       </c>
       <c r="G74" s="31" t="n">
         <f aca="false">G52*(G51+G66)+G56*(G53+G73)+G55*(G54+G69)</f>
-        <v>1.22796501622121</v>
+        <v>1.22796543477806</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>746</v>
@@ -62876,15 +63167,15 @@
       </c>
       <c r="D76" s="48" t="n">
         <f aca="false">D72/D75</f>
-        <v>0.0151286660819127</v>
+        <v>0.0151286680480646</v>
       </c>
       <c r="E76" s="48" t="n">
         <f aca="false">E72/E75</f>
-        <v>0.0390720132259518</v>
+        <v>0.0390720204985508</v>
       </c>
       <c r="F76" s="48" t="n">
         <f aca="false">F72/F75</f>
-        <v>0.0271906077511186</v>
+        <v>0.0271906182360654</v>
       </c>
       <c r="G76" s="48" t="n">
         <f aca="false">G72/G75</f>
@@ -62904,19 +63195,19 @@
       </c>
       <c r="D77" s="49" t="n">
         <f aca="false">C77+D76</f>
-        <v>0.0151286660819127</v>
+        <v>0.0151286680480646</v>
       </c>
       <c r="E77" s="49" t="n">
         <f aca="false">D77+E76</f>
-        <v>0.0542006793078645</v>
+        <v>0.0542006885466154</v>
       </c>
       <c r="F77" s="49" t="n">
         <f aca="false">E77+F76</f>
-        <v>0.0813912870589831</v>
+        <v>0.0813913067826808</v>
       </c>
       <c r="G77" s="49" t="n">
         <f aca="false">F77+G76</f>
-        <v>0.150013509281205</v>
+        <v>0.150013529004903</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -63000,7 +63291,7 @@
       </c>
       <c r="G80" s="31" t="n">
         <f aca="false">G53+G73</f>
-        <v>0.167607385176778</v>
+        <v>0.16761087315047</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -63056,7 +63347,7 @@
       </c>
       <c r="G82" s="35" t="n">
         <f aca="false">G62+G78+G81+G80</f>
-        <v>35.1634093851768</v>
+        <v>35.1634128731505</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -63072,19 +63363,19 @@
       </c>
       <c r="D83" s="35" t="n">
         <f aca="false">C83+D35+D36-D50</f>
-        <v>-16.6038711989053</v>
+        <v>-16.6038716410595</v>
       </c>
       <c r="E83" s="35" t="n">
         <f aca="false">D83+E35+E36-E50</f>
-        <v>-30.442291619197</v>
+        <v>-30.4422936968351</v>
       </c>
       <c r="F83" s="35" t="n">
         <f aca="false">E83+F35+F36-F50</f>
-        <v>-40.4541449320919</v>
+        <v>-40.4541493676162</v>
       </c>
       <c r="G83" s="35" t="n">
         <f aca="false">F83+G35+G36-G50</f>
-        <v>-59.8257585010474</v>
+        <v>-59.8257660059886</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>756</v>
@@ -63117,7 +63408,7 @@
       </c>
       <c r="C87" s="50" t="n">
         <f aca="false">SUM(C45:G45)</f>
-        <v>-77.7820973928621</v>
+        <v>-77.7821053163601</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -63162,7 +63453,7 @@
       </c>
       <c r="C92" s="50" t="n">
         <f aca="false">SUM(C38:G38)+SUM(C39:G39)+SUM(C40:G40)+SUM(C41:G41)</f>
-        <v>66.0238973928621</v>
+        <v>66.0239053163601</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -64508,27 +64799,27 @@
       <c r="B41" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="38" t="str">
+      <c r="C41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!C$286),輸入與假設!C$286,"")</f>
         <v/>
       </c>
-      <c r="D41" s="38" t="str">
+      <c r="D41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!D$286),輸入與假設!D$286,"")</f>
         <v/>
       </c>
-      <c r="E41" s="38" t="str">
+      <c r="E41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!E$286),輸入與假設!E$286,"")</f>
         <v/>
       </c>
-      <c r="F41" s="38" t="str">
+      <c r="F41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!F$286),輸入與假設!F$286,"")</f>
         <v/>
       </c>
-      <c r="G41" s="38" t="str">
+      <c r="G41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!G$286),輸入與假設!G$286,"")</f>
         <v/>
       </c>
-      <c r="H41" s="38" t="str">
+      <c r="H41" s="58" t="str">
         <f aca="false">IF(ISNUMBER(輸入與假設!H$286),輸入與假設!H$286,"")</f>
         <v/>
       </c>
@@ -67829,19 +68120,19 @@
       </c>
       <c r="D36" s="66" t="n">
         <f aca="false">輸入與假設!D$53+各期收支!D15/MAX(0.01,D35)</f>
-        <v>0.550886349310725</v>
+        <v>0.550894533258511</v>
       </c>
       <c r="E36" s="66" t="n">
         <f aca="false">輸入與假設!E$53+各期收支!E15/MAX(0.01,E35)</f>
-        <v>0.528396597709424</v>
+        <v>0.52840615351849</v>
       </c>
       <c r="F36" s="66" t="n">
         <f aca="false">輸入與假設!F$53+各期收支!F15/MAX(0.01,F35)</f>
-        <v>0.505995148894921</v>
+        <v>0.506001992869976</v>
       </c>
       <c r="G36" s="66" t="n">
         <f aca="false">輸入與假設!G$53+各期收支!G15/MAX(0.01,G35)</f>
-        <v>0.492844638294965</v>
+        <v>0.492850278687208</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>993</v>
@@ -67860,19 +68151,19 @@
       </c>
       <c r="D37" s="35" t="n">
         <f aca="false">D33*D36</f>
-        <v>3.69896300435364</v>
+        <v>3.69901795601495</v>
       </c>
       <c r="E37" s="35" t="n">
         <f aca="false">E33*E36</f>
-        <v>3.73565292703846</v>
+        <v>3.73572048460084</v>
       </c>
       <c r="F37" s="35" t="n">
         <f aca="false">F33*F36</f>
-        <v>3.75607222237366</v>
+        <v>3.75612302615044</v>
       </c>
       <c r="G37" s="35" t="n">
         <f aca="false">G33*G36</f>
-        <v>2.91937250904087</v>
+        <v>2.9194059199878</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>995</v>
@@ -67891,19 +68182,19 @@
       </c>
       <c r="D38" s="60" t="n">
         <f aca="false">D23*(1-輸入與假設!D$44*(1-輸入與假設!D$45))*D36</f>
-        <v>2.22382161769426</v>
+        <v>2.2238546547082</v>
       </c>
       <c r="E38" s="60" t="n">
         <f aca="false">E23*(1-輸入與假設!E$44*(1-輸入與假設!E$45))*E36</f>
-        <v>8.23197479835494</v>
+        <v>8.23212366982714</v>
       </c>
       <c r="F38" s="60" t="n">
         <f aca="false">F23*(1-輸入與假設!F$44*(1-輸入與假設!F$45))*F36</f>
-        <v>13.5021471986569</v>
+        <v>13.5023298256224</v>
       </c>
       <c r="G38" s="60" t="n">
         <f aca="false">G23*(1-輸入與假設!G$44*(1-輸入與假設!G$45))*G36</f>
-        <v>18.2683215907122</v>
+        <v>18.2685306636967</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>997</v>
@@ -68344,19 +68635,19 @@
       </c>
       <c r="D24" s="60" t="n">
         <f aca="false">各期收支!D15</f>
-        <v>0.655200008842105</v>
+        <v>0.65528843967151</v>
       </c>
       <c r="E24" s="60" t="n">
         <f aca="false">各期收支!E15</f>
-        <v>1.02454484938882</v>
+        <v>1.02476291390728</v>
       </c>
       <c r="F24" s="60" t="n">
         <f aca="false">各期收支!F15</f>
-        <v>1.00755386972781</v>
+        <v>1.00778965835642</v>
       </c>
       <c r="G24" s="60" t="n">
         <f aca="false">各期收支!G15</f>
-        <v>0.994536759243649</v>
+        <v>0.994782312591867</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -68428,19 +68719,19 @@
       </c>
       <c r="D27" s="35" t="n">
         <f aca="false">D24/D26/D25*1000</f>
-        <v>0.630000008502024</v>
+        <v>0.630085038145682</v>
       </c>
       <c r="E27" s="35" t="n">
         <f aca="false">E24/E26/E25*1000</f>
-        <v>0.632435092215323</v>
+        <v>0.632569699942768</v>
       </c>
       <c r="F27" s="35" t="n">
         <f aca="false">F24/F26/F25*1000</f>
-        <v>0.45797903169446</v>
+        <v>0.458086208343826</v>
       </c>
       <c r="G27" s="35" t="n">
         <f aca="false">G24/G26/G25*1000</f>
-        <v>0.357747035699154</v>
+        <v>0.357835364241679</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>1054</v>
@@ -68501,19 +68792,19 @@
       </c>
       <c r="D30" s="35" t="n">
         <f aca="false">D29-D24</f>
-        <v>-0.655200008842105</v>
+        <v>-0.65528843967151</v>
       </c>
       <c r="E30" s="35" t="n">
         <f aca="false">E29-E24</f>
-        <v>-1.02454484938882</v>
+        <v>-1.02476291390728</v>
       </c>
       <c r="F30" s="35" t="n">
         <f aca="false">F29-F24</f>
-        <v>-1.00755386972781</v>
+        <v>-1.00778965835642</v>
       </c>
       <c r="G30" s="35" t="n">
         <f aca="false">G29-G24</f>
-        <v>-0.994536759243649</v>
+        <v>-0.994782312591867</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>1060</v>
@@ -68525,7 +68816,7 @@
       </c>
       <c r="C31" s="69" t="n">
         <f aca="false">SUM(C30:G30)</f>
-        <v>-3.82343548720239</v>
+        <v>-3.82422332452708</v>
       </c>
     </row>
   </sheetData>
@@ -69681,19 +69972,19 @@
       </c>
       <c r="D7" s="60" t="n">
         <f aca="false">各期收支!D83-各期收支!C83</f>
-        <v>-17.2688953312387</v>
+        <v>-17.2688957733928</v>
       </c>
       <c r="E7" s="60" t="n">
         <f aca="false">各期收支!E83-各期收支!D83</f>
-        <v>-13.8384204202917</v>
+        <v>-13.8384220557756</v>
       </c>
       <c r="F7" s="60" t="n">
         <f aca="false">各期收支!F83-各期收支!E83</f>
-        <v>-10.0118533128948</v>
+        <v>-10.0118556707811</v>
       </c>
       <c r="G7" s="60" t="n">
         <f aca="false">各期收支!G83-各期收支!F83</f>
-        <v>-19.3716135689556</v>
+        <v>-19.3716166383724</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>1147</v>
@@ -69780,7 +70071,7 @@
       </c>
       <c r="G10" s="60" t="n">
         <f aca="false">各期收支!G73</f>
-        <v>0.167607385176778</v>
+        <v>0.16761087315047</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -69796,15 +70087,15 @@
       </c>
       <c r="D11" s="60" t="n">
         <f aca="false">各期收支!D72</f>
-        <v>3.40217981449877</v>
+        <v>3.40218025665292</v>
       </c>
       <c r="E11" s="60" t="n">
         <f aca="false">各期收支!E72</f>
-        <v>8.78663155029171</v>
+        <v>8.7866331857756</v>
       </c>
       <c r="F11" s="60" t="n">
         <f aca="false">各期收支!F72</f>
-        <v>6.11470544289481</v>
+        <v>6.11470780078109</v>
       </c>
       <c r="G11" s="60" t="n">
         <f aca="false">各期收支!G72</f>
@@ -69836,7 +70127,7 @@
       </c>
       <c r="G12" s="60" t="n">
         <f aca="false">-各期收支!G74</f>
-        <v>-1.22796501622121</v>
+        <v>-1.22796543477806</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -70112,7 +70403,7 @@
       </c>
       <c r="G22" s="60" t="n">
         <f aca="false">各期收支!G80</f>
-        <v>0.167607385176778</v>
+        <v>0.16761087315047</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -70140,7 +70431,7 @@
       </c>
       <c r="G23" s="35" t="n">
         <f aca="false">SUM(G18:G22)</f>
-        <v>35.1634093851768</v>
+        <v>35.1634128731505</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>1168</v>
@@ -70171,7 +70462,7 @@
       </c>
       <c r="G24" s="35" t="n">
         <f aca="false">G23-G13</f>
-        <v>33.1634093851768</v>
+        <v>33.1634128731505</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70227,15 +70518,15 @@
       </c>
       <c r="D27" s="48" t="n">
         <f aca="false">各期收支!D76</f>
-        <v>0.0151286660819127</v>
+        <v>0.0151286680480646</v>
       </c>
       <c r="E27" s="48" t="n">
         <f aca="false">各期收支!E76</f>
-        <v>0.0390720132259518</v>
+        <v>0.0390720204985508</v>
       </c>
       <c r="F27" s="48" t="n">
         <f aca="false">各期收支!F76</f>
-        <v>0.0271906077511186</v>
+        <v>0.0271906182360654</v>
       </c>
       <c r="G27" s="48" t="n">
         <f aca="false">各期收支!G76</f>
@@ -70255,19 +70546,19 @@
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">損益!D21</f>
-        <v>0.339339353156743</v>
+        <v>0.339339355122895</v>
       </c>
       <c r="E28" s="49" t="n">
         <f aca="false">損益!E21</f>
-        <v>0.381653473253443</v>
+        <v>0.381653482492194</v>
       </c>
       <c r="F28" s="49" t="n">
         <f aca="false">損益!F21</f>
-        <v>0.412118608944017</v>
+        <v>0.412118628667715</v>
       </c>
       <c r="G28" s="49" t="n">
         <f aca="false">損益!G21</f>
-        <v>0.48404810438509</v>
+        <v>0.484048124108787</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>1174</v>
@@ -70366,7 +70657,7 @@
       </c>
       <c r="G32" s="74" t="n">
         <f aca="false">G23/MAX(0.01,G30)</f>
-        <v>1.00143397892536</v>
+        <v>1.00143407826087</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>1177</v>
@@ -70397,7 +70688,7 @@
       </c>
       <c r="G33" s="75" t="n">
         <f aca="false">G23/MAX(0.01,損益!G19/輸入與假設!G$37)</f>
-        <v>1.71852781336568</v>
+        <v>1.71852798383208</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>1179</v>
